--- a/resources/table/enum.clan.xlsx
+++ b/resources/table/enum.clan.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cshyeon\git\fb\resources\table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E39AC127-F089-4CEC-80CD-084B16786496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6103E65-355A-4D53-91CC-C03884FA36C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
+    <workbookView xWindow="38280" yWindow="-135" windowWidth="38640" windowHeight="21120" xr2:uid="{E3DF90E4-1439-4BA6-8481-C5727015A5CB}"/>
   </bookViews>
   <sheets>
-    <sheet name="CLAN_POSITION" sheetId="1" r:id="rId1"/>
+    <sheet name="CLAN_ROLE" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -118,7 +118,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
